--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260827.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>372,192,194</t>
+          <t>26,558,536</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>26,558,536</t>
+          <t>372,192,194</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>260,943,407</t>
+          <t>115,173,712</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>115,173,712</t>
+          <t>260,943,407</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>216,330,460</t>
+          <t>17,738,440</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>17,738,440</t>
+          <t>216,330,460</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,326,047</t>
+          <t>7,996,031</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,996,031</t>
+          <t>1,326,047</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
